--- a/Dachukunnavi_V1.xlsx
+++ b/Dachukunnavi_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\autofas1\users\sai.datla\My Documents\Sai Datla\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\K157411\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D662A53-7202-4B19-9844-41CAAB311A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF3D79E-D0B5-4C6C-8744-702931651F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUDHA" sheetId="6" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="KKD_Plot4Plans" sheetId="17" r:id="rId11"/>
     <sheet name="kkd_Plot5_Plans" sheetId="15" r:id="rId12"/>
     <sheet name="Kesanakuru" sheetId="16" r:id="rId13"/>
+    <sheet name="kkd_Plot6Plans" sheetId="18" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'FAMILY SAVINGS'!$B$2:$C$7</definedName>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="464">
   <si>
     <t>Receiver</t>
   </si>
@@ -1333,6 +1334,190 @@
   </si>
   <si>
     <t>Confirmed (Video)</t>
+  </si>
+  <si>
+    <r>
+      <t>TransferWise</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CASH)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sai HDFC Bank NRI Account </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CASH)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TransferWise</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (CASH)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sudha Barclays - Via Transferwise </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(CASH)</t>
+    </r>
+  </si>
+  <si>
+    <t>Jay (10lks) + Komal (2 Lks)</t>
+  </si>
+  <si>
+    <t>Mamiya 4m mom</t>
+  </si>
+  <si>
+    <t>Sudha HDFC</t>
+  </si>
+  <si>
+    <t>Sudha Barclays</t>
+  </si>
+  <si>
+    <t>Per Cent Cost</t>
+  </si>
+  <si>
+    <t>Total Cents</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Total with me</t>
+  </si>
+  <si>
+    <t>Total Requirement Further</t>
+  </si>
+  <si>
+    <t>Komal (Cash)</t>
+  </si>
+  <si>
+    <t>Mammu (Cash)</t>
+  </si>
+  <si>
+    <t>Jay Cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available - Further </t>
+  </si>
+  <si>
+    <t>Chowdary</t>
+  </si>
+  <si>
+    <t>Pending to send for Land Owner</t>
+  </si>
+  <si>
+    <t>Commission</t>
+  </si>
+  <si>
+    <t>Bank Transfer</t>
+  </si>
+  <si>
+    <t>Cash Rest</t>
+  </si>
+  <si>
+    <t>2 cents will be given later end of month</t>
+  </si>
+  <si>
+    <t>Total Cash Available:</t>
+  </si>
+  <si>
+    <t>Cash Required Now</t>
+  </si>
+  <si>
+    <t>Cash WithDrawn (FIL)</t>
+  </si>
+  <si>
+    <t>Cash WithDrawn (MIL)</t>
+  </si>
+  <si>
+    <t>Sai Halifax</t>
+  </si>
+  <si>
+    <t>Sankranthi Celebrations</t>
+  </si>
+  <si>
+    <t>Cash +Transfers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone from Vijayawada </t>
+  </si>
+  <si>
+    <t>Transfer to HDFC 153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Shop </t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>Cash in KKD</t>
+  </si>
+  <si>
+    <t>Amount (In Lacs)</t>
+  </si>
+  <si>
+    <t>HDFC Bank - Self</t>
+  </si>
+  <si>
+    <t>HDFC Bank - Sudha</t>
+  </si>
+  <si>
+    <t>HDFC Bank - Attatiya</t>
+  </si>
+  <si>
+    <t>Halifax</t>
+  </si>
+  <si>
+    <t>Barclays</t>
+  </si>
+  <si>
+    <t>Komal</t>
+  </si>
+  <si>
+    <t>Lavanya</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1528,7 @@
     <numFmt numFmtId="164" formatCode="0.00;[Red]0.00"/>
     <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1372,13 +1557,6 @@
       <strike/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1872,7 +2050,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1982,7 +2160,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2037,7 +2214,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2054,7 +2231,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2072,6 +2249,8 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2114,32 +2293,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2150,22 +2323,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2192,13 +2371,13 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2266,6 +2445,12 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2551,7 +2736,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" customWidth="1"/>
     <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.7109375" customWidth="1"/>
@@ -2571,10 +2756,10 @@
       <c r="E2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="57">
+      <c r="J2" s="56">
         <v>1000000</v>
       </c>
     </row>
@@ -2582,7 +2767,7 @@
       <c r="B3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="16">
         <v>120000</v>
       </c>
       <c r="D3" s="21">
@@ -2591,10 +2776,10 @@
       <c r="E3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="58" t="s">
+      <c r="I3" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="59">
+      <c r="J3" s="58">
         <v>950000</v>
       </c>
     </row>
@@ -2611,10 +2796,10 @@
       <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="58" t="s">
+      <c r="I4" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="59">
+      <c r="J4" s="58">
         <v>200000</v>
       </c>
     </row>
@@ -2622,7 +2807,7 @@
       <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="51">
+      <c r="C5" s="97">
         <v>55000</v>
       </c>
       <c r="D5" s="21">
@@ -2631,10 +2816,10 @@
       <c r="E5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="58" t="s">
+      <c r="I5" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="59">
+      <c r="J5" s="58">
         <v>-650000</v>
       </c>
     </row>
@@ -2651,10 +2836,10 @@
       <c r="E6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="58" t="s">
+      <c r="I6" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="58">
         <v>350000</v>
       </c>
     </row>
@@ -2671,10 +2856,10 @@
       <c r="E7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="58" t="s">
+      <c r="I7" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="59">
+      <c r="J7" s="58">
         <v>50000</v>
       </c>
     </row>
@@ -2691,12 +2876,12 @@
       <c r="E8" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="58" t="s">
+      <c r="I8" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="59">
+      <c r="J8" s="58">
         <f>C22</f>
-        <v>1610000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2712,10 +2897,10 @@
       <c r="E9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="60" t="s">
+      <c r="I9" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="61">
+      <c r="J9" s="60">
         <v>400000</v>
       </c>
     </row>
@@ -2732,12 +2917,12 @@
       <c r="E10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="54" t="s">
+      <c r="I10" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="55">
+      <c r="J10" s="54">
         <f>J8+J6+J5+J4+J3+J2+J7+J9</f>
-        <v>3910000</v>
+        <v>4800000</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
@@ -2822,48 +3007,72 @@
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="6"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="11"/>
+      <c r="B17" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="C17" s="11">
+        <v>700000</v>
+      </c>
+      <c r="D17" s="21">
+        <v>46030</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="11"/>
+      <c r="B18" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="C18" s="11">
+        <v>60000</v>
+      </c>
+      <c r="D18" s="21">
+        <v>46090</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="11"/>
+      <c r="B19" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="C19" s="11">
+        <v>130000</v>
+      </c>
+      <c r="D19" s="21">
+        <v>46107</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="52"/>
+      <c r="B20" s="51"/>
       <c r="D20" s="1"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C21">
-        <f>SUM(C3:C16)</f>
-        <v>1785000</v>
+        <f>SUM(C3:C19)</f>
+        <v>2675000</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="53">
+      <c r="C22" s="52">
         <f>C21-C3-C5</f>
-        <v>1610000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="85" t="s">
+      <c r="B24" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="85">
-        <v>150000</v>
+      <c r="C24" s="84">
+        <v>1500000</v>
       </c>
       <c r="E24" s="1"/>
     </row>
@@ -2910,7 +3119,7 @@
       <c r="C4" s="12">
         <v>1</v>
       </c>
-      <c r="D4" s="88">
+      <c r="D4" s="87">
         <v>45551</v>
       </c>
       <c r="E4" s="22" t="s">
@@ -2930,7 +3139,7 @@
       <c r="C5" s="12">
         <v>2</v>
       </c>
-      <c r="D5" s="84">
+      <c r="D5" s="83">
         <v>45567</v>
       </c>
       <c r="E5" s="22" t="s">
@@ -2950,7 +3159,7 @@
       <c r="C6" s="12">
         <v>2</v>
       </c>
-      <c r="D6" s="84">
+      <c r="D6" s="83">
         <v>45652</v>
       </c>
       <c r="E6" s="22" t="s">
@@ -2977,7 +3186,7 @@
       <c r="C7" s="12">
         <v>3</v>
       </c>
-      <c r="D7" s="84">
+      <c r="D7" s="83">
         <v>45573</v>
       </c>
       <c r="E7" s="22" t="s">
@@ -2993,13 +3202,13 @@
         <v>308</v>
       </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="91"/>
+      <c r="J7" s="90"/>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C8" s="12">
         <v>4</v>
       </c>
-      <c r="D8" s="84">
+      <c r="D8" s="83">
         <v>45605</v>
       </c>
       <c r="E8" s="22" t="s">
@@ -3015,7 +3224,7 @@
         <v>308</v>
       </c>
       <c r="I8" s="2"/>
-      <c r="J8" s="91"/>
+      <c r="J8" s="90"/>
       <c r="K8" t="s">
         <v>335</v>
       </c>
@@ -3030,7 +3239,7 @@
       <c r="C9" s="12">
         <v>5</v>
       </c>
-      <c r="D9" s="84">
+      <c r="D9" s="83">
         <v>45635</v>
       </c>
       <c r="E9" s="22" t="s">
@@ -3046,7 +3255,7 @@
         <v>308</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="91"/>
+      <c r="J9" s="90"/>
       <c r="L9">
         <f>G15</f>
         <v>49000</v>
@@ -3056,7 +3265,7 @@
       <c r="C10" s="12">
         <v>6</v>
       </c>
-      <c r="D10" s="84">
+      <c r="D10" s="83">
         <v>45645</v>
       </c>
       <c r="E10" s="22" t="s">
@@ -3072,11 +3281,11 @@
         <v>308</v>
       </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="91"/>
+      <c r="J10" s="90"/>
     </row>
     <row r="11" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C11" s="12"/>
-      <c r="D11" s="84">
+      <c r="D11" s="83">
         <v>45649</v>
       </c>
       <c r="E11" s="22" t="s">
@@ -3092,13 +3301,13 @@
         <v>308</v>
       </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="91"/>
+      <c r="J11" s="90"/>
     </row>
     <row r="12" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C12" s="12">
         <v>7</v>
       </c>
-      <c r="D12" s="84">
+      <c r="D12" s="83">
         <v>45660</v>
       </c>
       <c r="E12" s="22" t="s">
@@ -3114,11 +3323,11 @@
         <v>308</v>
       </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="91"/>
+      <c r="J12" s="90"/>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C13" s="12"/>
-      <c r="D13" s="84"/>
+      <c r="D13" s="83"/>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
       <c r="G13" s="22"/>
@@ -3127,7 +3336,7 @@
         <f>SUM(G7:G13)</f>
         <v>480000</v>
       </c>
-      <c r="J13" s="91" t="s">
+      <c r="J13" s="90" t="s">
         <v>352</v>
       </c>
       <c r="L13">
@@ -3136,12 +3345,12 @@
       </c>
     </row>
     <row r="14" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="147"/>
-      <c r="D14" s="148"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="148"/>
-      <c r="G14" s="148"/>
-      <c r="H14" s="149"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="149"/>
+      <c r="E14" s="149"/>
+      <c r="F14" s="149"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="150"/>
       <c r="L14">
         <f>G17</f>
         <v>500000</v>
@@ -3151,7 +3360,7 @@
       <c r="C15" s="12">
         <v>1</v>
       </c>
-      <c r="D15" s="88">
+      <c r="D15" s="87">
         <v>45551</v>
       </c>
       <c r="E15" s="22" t="s">
@@ -3175,7 +3384,7 @@
       <c r="C16" s="12">
         <v>2</v>
       </c>
-      <c r="D16" s="88">
+      <c r="D16" s="87">
         <v>45552</v>
       </c>
       <c r="E16" s="22" t="s">
@@ -3199,7 +3408,7 @@
       <c r="C17" s="12">
         <v>3</v>
       </c>
-      <c r="D17" s="88">
+      <c r="D17" s="87">
         <v>45552</v>
       </c>
       <c r="E17" s="22" t="s">
@@ -3223,7 +3432,7 @@
       <c r="C18" s="12">
         <v>4</v>
       </c>
-      <c r="D18" s="88">
+      <c r="D18" s="87">
         <v>45551</v>
       </c>
       <c r="E18" s="22" t="s">
@@ -3247,7 +3456,7 @@
       <c r="C19" s="12">
         <v>5</v>
       </c>
-      <c r="D19" s="88">
+      <c r="D19" s="87">
         <v>45551</v>
       </c>
       <c r="E19" s="22" t="s">
@@ -3273,7 +3482,7 @@
       <c r="C20" s="12">
         <v>6</v>
       </c>
-      <c r="D20" s="88">
+      <c r="D20" s="87">
         <v>45552</v>
       </c>
       <c r="E20" s="22" t="s">
@@ -3299,7 +3508,7 @@
       <c r="C21" s="12">
         <v>7</v>
       </c>
-      <c r="D21" s="88">
+      <c r="D21" s="87">
         <v>45565</v>
       </c>
       <c r="E21" s="22" t="s">
@@ -3323,7 +3532,7 @@
       <c r="C22" s="12">
         <v>8</v>
       </c>
-      <c r="D22" s="84">
+      <c r="D22" s="83">
         <v>45567</v>
       </c>
       <c r="E22" s="22" t="s">
@@ -3347,7 +3556,7 @@
       <c r="C23" s="12">
         <v>9</v>
       </c>
-      <c r="D23" s="84">
+      <c r="D23" s="83">
         <v>45568</v>
       </c>
       <c r="E23" s="22" t="s">
@@ -3371,7 +3580,7 @@
       <c r="C24" s="12">
         <v>10</v>
       </c>
-      <c r="D24" s="88">
+      <c r="D24" s="87">
         <v>45575</v>
       </c>
       <c r="E24" s="22" t="s">
@@ -3395,7 +3604,7 @@
       <c r="C25" s="12">
         <v>11</v>
       </c>
-      <c r="D25" s="88">
+      <c r="D25" s="87">
         <v>45588</v>
       </c>
       <c r="E25" s="22" t="s">
@@ -3419,16 +3628,16 @@
       <c r="C26" s="12">
         <v>12</v>
       </c>
-      <c r="D26" s="88">
+      <c r="D26" s="87">
         <v>45600</v>
       </c>
       <c r="E26" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="F26" s="92" t="s">
+      <c r="F26" s="91" t="s">
         <v>353</v>
       </c>
-      <c r="G26" s="93">
+      <c r="G26" s="92">
         <v>49000</v>
       </c>
       <c r="H26" s="14" t="s">
@@ -3443,16 +3652,16 @@
       <c r="C27" s="12">
         <v>13</v>
       </c>
-      <c r="D27" s="88">
+      <c r="D27" s="87">
         <v>45601</v>
       </c>
       <c r="E27" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="F27" s="92" t="s">
+      <c r="F27" s="91" t="s">
         <v>353</v>
       </c>
-      <c r="G27" s="93">
+      <c r="G27" s="92">
         <v>451000</v>
       </c>
       <c r="H27" s="14" t="s">
@@ -3467,13 +3676,13 @@
       <c r="C28" s="12">
         <v>14</v>
       </c>
-      <c r="D28" s="88">
+      <c r="D28" s="87">
         <v>45602</v>
       </c>
       <c r="E28" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="F28" s="92" t="s">
+      <c r="F28" s="91" t="s">
         <v>353</v>
       </c>
       <c r="G28" s="22">
@@ -3491,7 +3700,7 @@
       <c r="C29" s="12">
         <v>15</v>
       </c>
-      <c r="D29" s="88">
+      <c r="D29" s="87">
         <v>45602</v>
       </c>
       <c r="E29" s="22" t="s">
@@ -3515,7 +3724,7 @@
       <c r="C30" s="12">
         <v>16</v>
       </c>
-      <c r="D30" s="88">
+      <c r="D30" s="87">
         <v>45602</v>
       </c>
       <c r="E30" s="22" t="s">
@@ -3539,13 +3748,13 @@
       <c r="C31" s="12">
         <v>16</v>
       </c>
-      <c r="D31" s="88">
+      <c r="D31" s="87">
         <v>45602</v>
       </c>
       <c r="E31" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="F31" s="92" t="s">
+      <c r="F31" s="91" t="s">
         <v>353</v>
       </c>
       <c r="G31" s="22">
@@ -3563,13 +3772,13 @@
       <c r="C32" s="12">
         <v>17</v>
       </c>
-      <c r="D32" s="88">
+      <c r="D32" s="87">
         <v>45603</v>
       </c>
       <c r="E32" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="F32" s="92" t="s">
+      <c r="F32" s="91" t="s">
         <v>353</v>
       </c>
       <c r="G32" s="22">
@@ -3587,13 +3796,13 @@
       <c r="C33" s="12">
         <v>18</v>
       </c>
-      <c r="D33" s="88">
+      <c r="D33" s="87">
         <v>45603</v>
       </c>
       <c r="E33" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="F33" s="92" t="s">
+      <c r="F33" s="91" t="s">
         <v>353</v>
       </c>
       <c r="G33" s="22">
@@ -3611,7 +3820,7 @@
       <c r="C34" s="12">
         <v>19</v>
       </c>
-      <c r="D34" s="88">
+      <c r="D34" s="87">
         <v>45603</v>
       </c>
       <c r="E34" s="22" t="s">
@@ -3635,13 +3844,13 @@
       <c r="C35" s="12">
         <v>20</v>
       </c>
-      <c r="D35" s="88">
+      <c r="D35" s="87">
         <v>45614</v>
       </c>
       <c r="E35" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="F35" s="92" t="s">
+      <c r="F35" s="91" t="s">
         <v>354</v>
       </c>
       <c r="G35" s="22">
@@ -3659,13 +3868,13 @@
       <c r="C36" s="12">
         <v>21</v>
       </c>
-      <c r="D36" s="88">
+      <c r="D36" s="87">
         <v>45614</v>
       </c>
       <c r="E36" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="F36" s="92" t="s">
+      <c r="F36" s="91" t="s">
         <v>354</v>
       </c>
       <c r="G36" s="22">
@@ -3683,13 +3892,13 @@
       <c r="C37" s="12">
         <v>22</v>
       </c>
-      <c r="D37" s="88">
+      <c r="D37" s="87">
         <v>45615</v>
       </c>
       <c r="E37" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="F37" s="92" t="s">
+      <c r="F37" s="91" t="s">
         <v>354</v>
       </c>
       <c r="G37" s="22">
@@ -3707,13 +3916,13 @@
       <c r="C38" s="12">
         <v>23</v>
       </c>
-      <c r="D38" s="88">
+      <c r="D38" s="87">
         <v>45620</v>
       </c>
       <c r="E38" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="F38" s="92" t="s">
+      <c r="F38" s="91" t="s">
         <v>353</v>
       </c>
       <c r="G38" s="22">
@@ -3746,13 +3955,13 @@
       <c r="C39" s="12">
         <v>24</v>
       </c>
-      <c r="D39" s="88">
+      <c r="D39" s="87">
         <v>45620</v>
       </c>
       <c r="E39" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="F39" s="92" t="s">
+      <c r="F39" s="91" t="s">
         <v>353</v>
       </c>
       <c r="G39" s="22">
@@ -3772,7 +3981,7 @@
       <c r="C40" s="12">
         <v>25</v>
       </c>
-      <c r="D40" s="88">
+      <c r="D40" s="87">
         <v>45621</v>
       </c>
       <c r="E40" s="22" t="s">
@@ -3800,7 +4009,7 @@
       <c r="C41" s="12">
         <v>25</v>
       </c>
-      <c r="D41" s="88">
+      <c r="D41" s="87">
         <v>45621</v>
       </c>
       <c r="E41" s="22" t="s">
@@ -3828,13 +4037,13 @@
       <c r="C42" s="12">
         <v>26</v>
       </c>
-      <c r="D42" s="88">
+      <c r="D42" s="87">
         <v>45621</v>
       </c>
-      <c r="E42" s="150" t="s">
+      <c r="E42" s="151" t="s">
         <v>317</v>
       </c>
-      <c r="F42" s="151"/>
+      <c r="F42" s="152"/>
       <c r="G42" s="22">
         <v>3300000</v>
       </c>
@@ -3854,8 +4063,8 @@
       </c>
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="G43" s="95"/>
-      <c r="H43" s="95"/>
+      <c r="G43" s="94"/>
+      <c r="H43" s="94"/>
       <c r="J43" s="2">
         <f>J41-J42</f>
         <v>3504800</v>
@@ -3869,16 +4078,16 @@
       </c>
     </row>
     <row r="44" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="G44" s="95"/>
-      <c r="H44" s="95"/>
+      <c r="G44" s="94"/>
+      <c r="H44" s="94"/>
     </row>
     <row r="45" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C45" s="152" t="s">
+      <c r="C45" s="153" t="s">
         <v>345</v>
       </c>
-      <c r="D45" s="153"/>
-      <c r="E45" s="153"/>
-      <c r="F45" s="154"/>
+      <c r="D45" s="154"/>
+      <c r="E45" s="154"/>
+      <c r="F45" s="155"/>
       <c r="G45" s="22">
         <v>406</v>
       </c>
@@ -3887,12 +4096,12 @@
       </c>
     </row>
     <row r="46" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C46" s="152" t="s">
+      <c r="C46" s="153" t="s">
         <v>346</v>
       </c>
-      <c r="D46" s="153"/>
-      <c r="E46" s="153"/>
-      <c r="F46" s="154"/>
+      <c r="D46" s="154"/>
+      <c r="E46" s="154"/>
+      <c r="F46" s="155"/>
       <c r="G46" s="22">
         <v>35000</v>
       </c>
@@ -3901,27 +4110,27 @@
       </c>
     </row>
     <row r="47" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C47" s="145" t="s">
+      <c r="C47" s="146" t="s">
         <v>348</v>
       </c>
-      <c r="D47" s="145"/>
-      <c r="E47" s="145"/>
-      <c r="F47" s="145"/>
-      <c r="G47" s="89">
+      <c r="D47" s="146"/>
+      <c r="E47" s="146"/>
+      <c r="F47" s="146"/>
+      <c r="G47" s="88">
         <f>G46*G45</f>
         <v>14210000</v>
       </c>
-      <c r="H47" s="90" t="s">
+      <c r="H47" s="89" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="48" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C48" s="145" t="s">
+      <c r="C48" s="146" t="s">
         <v>349</v>
       </c>
-      <c r="D48" s="145"/>
-      <c r="E48" s="145"/>
-      <c r="F48" s="145"/>
+      <c r="D48" s="146"/>
+      <c r="E48" s="146"/>
+      <c r="F48" s="146"/>
       <c r="G48" s="16">
         <f>I38+I6+G42</f>
         <v>13993200</v>
@@ -3931,12 +4140,12 @@
       </c>
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C49" s="145" t="s">
+      <c r="C49" s="146" t="s">
         <v>366</v>
       </c>
-      <c r="D49" s="145"/>
-      <c r="E49" s="145"/>
-      <c r="F49" s="145"/>
+      <c r="D49" s="146"/>
+      <c r="E49" s="146"/>
+      <c r="F49" s="146"/>
       <c r="G49" s="16">
         <f>900000+100000</f>
         <v>1000000</v>
@@ -3946,12 +4155,12 @@
       </c>
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C50" s="145" t="s">
+      <c r="C50" s="146" t="s">
         <v>350</v>
       </c>
-      <c r="D50" s="145"/>
-      <c r="E50" s="145"/>
-      <c r="F50" s="145"/>
+      <c r="D50" s="146"/>
+      <c r="E50" s="146"/>
+      <c r="F50" s="146"/>
       <c r="G50" s="50">
         <f>G47-G48</f>
         <v>216800</v>
@@ -3961,12 +4170,12 @@
       </c>
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C51" s="145" t="s">
+      <c r="C51" s="146" t="s">
         <v>368</v>
       </c>
-      <c r="D51" s="145"/>
-      <c r="E51" s="145"/>
-      <c r="F51" s="145"/>
+      <c r="D51" s="146"/>
+      <c r="E51" s="146"/>
+      <c r="F51" s="146"/>
       <c r="G51" s="13">
         <f>30000+30000+140000</f>
         <v>200000</v>
@@ -3976,17 +4185,17 @@
       </c>
     </row>
     <row r="53" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C53" s="146" t="s">
+      <c r="C53" s="147" t="s">
         <v>369</v>
       </c>
-      <c r="D53" s="146"/>
-      <c r="E53" s="146"/>
-      <c r="F53" s="146"/>
-      <c r="G53" s="85">
+      <c r="D53" s="147"/>
+      <c r="E53" s="147"/>
+      <c r="F53" s="147"/>
+      <c r="G53" s="84">
         <f>G47+G49+G51</f>
         <v>15410000</v>
       </c>
-      <c r="H53" s="85" t="s">
+      <c r="H53" s="84" t="s">
         <v>351</v>
       </c>
     </row>
@@ -4022,10 +4231,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="101" t="s">
+      <c r="B3" s="102" t="s">
         <v>386</v>
       </c>
-      <c r="C3" s="101"/>
+      <c r="C3" s="102"/>
       <c r="F3" s="11" t="s">
         <v>387</v>
       </c>
@@ -4082,7 +4291,7 @@
       <c r="B7" s="11">
         <v>40000</v>
       </c>
-      <c r="C7" s="96" t="s">
+      <c r="C7" s="95" t="s">
         <v>385</v>
       </c>
     </row>
@@ -4117,12 +4326,12 @@
       <c r="C10" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="E10" s="114" t="s">
+      <c r="E10" s="122" t="s">
         <v>399</v>
       </c>
-      <c r="F10" s="114"/>
-      <c r="G10" s="114"/>
-      <c r="H10" s="114"/>
+      <c r="F10" s="122"/>
+      <c r="G10" s="122"/>
+      <c r="H10" s="122"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
@@ -4233,12 +4442,12 @@
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E18" s="155" t="s">
+      <c r="E18" s="156" t="s">
         <v>400</v>
       </c>
-      <c r="F18" s="156"/>
-      <c r="G18" s="156"/>
-      <c r="H18" s="157"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="157"/>
+      <c r="H18" s="158"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="E19" s="4">
@@ -4331,14 +4540,15 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FF28C7-9CD4-47F1-994A-8ED014497192}">
-  <dimension ref="C1:H27"/>
+  <dimension ref="C1:K49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="37.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:8" x14ac:dyDescent="0.25">
@@ -4659,89 +4869,144 @@
         <v>419</v>
       </c>
     </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C17" s="4">
         <v>16</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="D17" s="5">
+        <v>45889</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="G17" s="11">
+        <v>400000</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C18" s="4">
-        <v>16</v>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="D18" s="5">
+        <v>45889</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="G18" s="11">
+        <v>400000</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C19" s="4">
-        <v>17</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="D19" s="5">
+        <v>45890</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="G19" s="11">
+        <v>49900</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C20" s="4">
-        <v>18</v>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="D20" s="5">
+        <v>45831</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="G20" s="11">
+        <v>450000</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C21" s="4">
-        <v>19</v>
-      </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="D21" s="5">
+        <v>45911</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="G21" s="11">
+        <f>1000000+200000</f>
+        <v>1200000</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C22" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="11"/>
       <c r="F22" s="6"/>
       <c r="G22" s="11"/>
       <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C23" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="11"/>
       <c r="F23" s="6"/>
       <c r="G23" s="11"/>
       <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C24" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="11"/>
       <c r="F24" s="6"/>
       <c r="G24" s="11"/>
       <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C25" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="11"/>
@@ -4749,9 +5014,9 @@
       <c r="G25" s="11"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C26" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="11"/>
@@ -4759,24 +5024,240 @@
       <c r="G26" s="11"/>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C27" s="158" t="s">
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C27" s="159" t="s">
         <v>364</v>
       </c>
-      <c r="D27" s="159"/>
-      <c r="E27" s="159"/>
-      <c r="F27" s="160"/>
-      <c r="G27" s="94">
+      <c r="D27" s="160"/>
+      <c r="E27" s="160"/>
+      <c r="F27" s="161"/>
+      <c r="G27" s="93">
         <f>SUM(G2:G26)</f>
-        <v>5500000</v>
+        <v>7999900</v>
       </c>
       <c r="H27" s="11"/>
+    </row>
+    <row r="29" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>434</v>
+      </c>
+      <c r="E29">
+        <v>500000</v>
+      </c>
+      <c r="F29" t="s">
+        <v>428</v>
+      </c>
+      <c r="G29">
+        <v>455000</v>
+      </c>
+    </row>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>425</v>
+      </c>
+      <c r="E30">
+        <v>500000</v>
+      </c>
+      <c r="F30" t="s">
+        <v>429</v>
+      </c>
+      <c r="G30">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>433</v>
+      </c>
+      <c r="E31">
+        <v>500000</v>
+      </c>
+      <c r="F31" t="s">
+        <v>430</v>
+      </c>
+      <c r="G31">
+        <f>G29*G30</f>
+        <v>15470000</v>
+      </c>
+    </row>
+    <row r="32" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>435</v>
+      </c>
+      <c r="E32">
+        <v>1000000</v>
+      </c>
+      <c r="F32" t="s">
+        <v>327</v>
+      </c>
+      <c r="G32">
+        <f>G27</f>
+        <v>7999900</v>
+      </c>
+    </row>
+    <row r="33" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>437</v>
+      </c>
+      <c r="E33">
+        <v>800000</v>
+      </c>
+      <c r="F33" t="s">
+        <v>431</v>
+      </c>
+      <c r="G33">
+        <f>SUM(E29:E37)</f>
+        <v>6300000</v>
+      </c>
+    </row>
+    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>445</v>
+      </c>
+      <c r="E34">
+        <v>700000</v>
+      </c>
+      <c r="F34" t="s">
+        <v>432</v>
+      </c>
+      <c r="G34" s="96">
+        <f>G31-G32-G33</f>
+        <v>1170100</v>
+      </c>
+    </row>
+    <row r="35" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>445</v>
+      </c>
+      <c r="E35">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="36" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>446</v>
+      </c>
+      <c r="E36">
+        <v>700000</v>
+      </c>
+      <c r="F36" t="s">
+        <v>436</v>
+      </c>
+      <c r="G36">
+        <f>SUM(E29:E39)</f>
+        <v>7200000</v>
+      </c>
+    </row>
+    <row r="37" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>426</v>
+      </c>
+      <c r="E37">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="38" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>447</v>
+      </c>
+      <c r="E38">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="39" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>427</v>
+      </c>
+      <c r="E39">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="40" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F40" t="s">
+        <v>438</v>
+      </c>
+      <c r="G40">
+        <f>G31-G32</f>
+        <v>7470100</v>
+      </c>
+      <c r="H40" t="s">
+        <v>440</v>
+      </c>
+      <c r="I40">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="41" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F41" t="s">
+        <v>439</v>
+      </c>
+      <c r="G41">
+        <v>150000</v>
+      </c>
+      <c r="H41" t="s">
+        <v>441</v>
+      </c>
+      <c r="I41">
+        <f>G40-I40</f>
+        <v>5970100</v>
+      </c>
+    </row>
+    <row r="42" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F42" t="s">
+        <v>366</v>
+      </c>
+      <c r="G42">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="43" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D43">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D44">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F47" t="s">
+        <v>443</v>
+      </c>
+      <c r="G47">
+        <f>2500000+800000</f>
+        <v>3300000</v>
+      </c>
+    </row>
+    <row r="48" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F48" t="s">
+        <v>444</v>
+      </c>
+      <c r="G48">
+        <f>I41-G47-G49</f>
+        <v>1760100</v>
+      </c>
+    </row>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F49" t="s">
+        <v>442</v>
+      </c>
+      <c r="G49">
+        <f>2*G29</f>
+        <v>910000</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C27:F27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4914,10 +5395,10 @@
       <c r="C19" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="161">
+      <c r="D19" s="162">
         <v>43275</v>
       </c>
-      <c r="E19" s="161"/>
+      <c r="E19" s="162"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
@@ -4965,7 +5446,7 @@
       <c r="D23" s="11">
         <v>98000</v>
       </c>
-      <c r="E23" s="65">
+      <c r="E23" s="64">
         <v>43678</v>
       </c>
     </row>
@@ -4979,7 +5460,7 @@
       <c r="D24" s="11">
         <v>75000</v>
       </c>
-      <c r="E24" s="65">
+      <c r="E24" s="64">
         <v>44075</v>
       </c>
     </row>
@@ -4993,7 +5474,7 @@
       <c r="D25" s="11">
         <v>350000</v>
       </c>
-      <c r="E25" s="65">
+      <c r="E25" s="64">
         <v>44986</v>
       </c>
     </row>
@@ -5036,10 +5517,10 @@
       <c r="E28" s="11"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="102" t="s">
+      <c r="B29" s="103" t="s">
         <v>380</v>
       </c>
-      <c r="C29" s="103"/>
+      <c r="C29" s="104"/>
       <c r="D29" s="13">
         <f>D28+D20</f>
         <v>767000</v>
@@ -5053,6 +5534,469 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D74F3B4-D06F-4A61-A651-3EB5BDD59A41}">
+  <dimension ref="B2:G40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="E2" s="163" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>45819</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="E3" s="4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5">
+        <v>45819</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="E4" s="4">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5">
+        <v>45819</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5">
+        <v>45819</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="E6" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5">
+        <v>45819</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="E7" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5">
+        <v>45819</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="E8" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5">
+        <v>45819</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="E9" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>45819</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="E10" s="4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>45819</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="110" t="s">
+        <v>463</v>
+      </c>
+      <c r="C12" s="164"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="9">
+        <f>SUM(E3:E11)</f>
+        <v>81.5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5">
+        <v>45819</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="4">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="4">
+        <v>3</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="4">
+        <v>4</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="4">
+        <v>5</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="4">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="4">
+        <v>7</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="4">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="4">
+        <v>9</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="4">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="4">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="4">
+        <v>12</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="4">
+        <v>13</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="4">
+        <v>14</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="4">
+        <v>15</v>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="4">
+        <v>16</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="4">
+        <v>17</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="4">
+        <v>18</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="4">
+        <v>19</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="4">
+        <v>20</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="4">
+        <v>21</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" s="4">
+        <v>22</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="4">
+        <v>23</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="4">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="4">
+        <v>25</v>
+      </c>
+      <c r="C39" s="5"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="159" t="s">
+        <v>364</v>
+      </c>
+      <c r="C40" s="160"/>
+      <c r="D40" s="160"/>
+      <c r="E40" s="161"/>
+      <c r="F40" s="93">
+        <f>SUM(F15:F39)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B12:D12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5080,11 +6024,11 @@
       </c>
     </row>
     <row r="3" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F3" s="97" t="s">
+      <c r="F3" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="98"/>
-      <c r="H3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="100"/>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -5093,11 +6037,11 @@
       <c r="C4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="100" t="s">
+      <c r="F4" s="101" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
       <c r="Q4" s="10" t="s">
         <v>35</v>
       </c>
@@ -5112,10 +6056,10 @@
       <c r="C5" s="7">
         <v>43275</v>
       </c>
-      <c r="F5" s="107" t="s">
+      <c r="F5" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="108"/>
+      <c r="G5" s="109"/>
       <c r="H5" s="26">
         <v>80000</v>
       </c>
@@ -5555,11 +6499,11 @@
       <c r="I25" t="s">
         <v>68</v>
       </c>
-      <c r="P25" s="101" t="s">
+      <c r="P25" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="Q25" s="101"/>
-      <c r="R25" s="101"/>
+      <c r="Q25" s="102"/>
+      <c r="R25" s="102"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F26" s="29">
@@ -5597,7 +6541,7 @@
       <c r="I27" t="s">
         <v>72</v>
       </c>
-      <c r="P27" s="104" t="s">
+      <c r="P27" s="105" t="s">
         <v>73</v>
       </c>
       <c r="Q27" s="11" t="s">
@@ -5624,7 +6568,7 @@
       <c r="I28" t="s">
         <v>75</v>
       </c>
-      <c r="P28" s="105"/>
+      <c r="P28" s="106"/>
       <c r="Q28" s="11" t="s">
         <v>76</v>
       </c>
@@ -5649,7 +6593,7 @@
       <c r="I29" t="s">
         <v>75</v>
       </c>
-      <c r="P29" s="106"/>
+      <c r="P29" s="107"/>
       <c r="Q29" s="11" t="s">
         <v>77</v>
       </c>
@@ -5752,11 +6696,11 @@
       <c r="C33" s="38">
         <v>44296</v>
       </c>
-      <c r="F33" s="101" t="s">
+      <c r="F33" s="102" t="s">
         <v>83</v>
       </c>
-      <c r="G33" s="101"/>
-      <c r="H33" s="101"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="102"/>
       <c r="P33" s="11" t="s">
         <v>84</v>
       </c>
@@ -5774,10 +6718,10 @@
       <c r="C34" s="41">
         <v>44</v>
       </c>
-      <c r="F34" s="109" t="s">
+      <c r="F34" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="G34" s="110"/>
+      <c r="G34" s="111"/>
       <c r="H34" s="4">
         <v>80000</v>
       </c>
@@ -5854,7 +6798,7 @@
       <c r="B37" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="C37" s="64">
+      <c r="C37" s="63">
         <v>600000</v>
       </c>
       <c r="D37" s="45" t="s">
@@ -5932,8 +6876,8 @@
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B40" s="62"/>
-      <c r="D40" s="63" t="s">
+      <c r="B40" s="61"/>
+      <c r="D40" s="62" t="s">
         <v>106</v>
       </c>
       <c r="F40" s="11"/>
@@ -5950,13 +6894,13 @@
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B41" s="78" t="s">
+      <c r="B41" s="77" t="s">
         <v>105</v>
       </c>
-      <c r="C41" s="63">
+      <c r="C41" s="62">
         <v>200000</v>
       </c>
-      <c r="D41" s="63" t="s">
+      <c r="D41" s="62" t="s">
         <v>109</v>
       </c>
       <c r="F41" s="11"/>
@@ -5973,11 +6917,11 @@
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B42" s="78"/>
-      <c r="C42" s="63">
+      <c r="B42" s="77"/>
+      <c r="C42" s="62">
         <v>300000</v>
       </c>
-      <c r="D42" s="63" t="s">
+      <c r="D42" s="62" t="s">
         <v>106</v>
       </c>
       <c r="F42" s="11"/>
@@ -5994,8 +6938,8 @@
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B43" s="78"/>
-      <c r="C43" s="63">
+      <c r="B43" s="77"/>
+      <c r="C43" s="62">
         <v>600000</v>
       </c>
       <c r="F43" s="11"/>
@@ -6071,10 +7015,10 @@
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B48" s="76" t="s">
+      <c r="B48" s="75" t="s">
         <v>121</v>
       </c>
-      <c r="C48" s="77"/>
+      <c r="C48" s="76"/>
       <c r="F48" s="11"/>
       <c r="G48" s="20"/>
       <c r="H48" s="11"/>
@@ -6219,10 +7163,10 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="18"/>
-      <c r="P57" s="102" t="s">
+      <c r="P57" s="103" t="s">
         <v>136</v>
       </c>
-      <c r="Q57" s="103"/>
+      <c r="Q57" s="104"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
@@ -6426,7 +7370,7 @@
       <c r="C79" s="28">
         <v>4</v>
       </c>
-      <c r="D79" s="74" t="s">
+      <c r="D79" s="73" t="s">
         <v>142</v>
       </c>
     </row>
@@ -6439,7 +7383,7 @@
         <f>(C78*C79)/100</f>
         <v>20000</v>
       </c>
-      <c r="D80" s="74"/>
+      <c r="D80" s="73"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="18"/>
@@ -6527,7 +7471,7 @@
       <c r="C90" s="40">
         <v>880000</v>
       </c>
-      <c r="D90" s="75" t="s">
+      <c r="D90" s="74" t="s">
         <v>143</v>
       </c>
     </row>
@@ -6538,7 +7482,7 @@
       <c r="C91" s="28">
         <v>6</v>
       </c>
-      <c r="D91" s="75"/>
+      <c r="D91" s="74"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B92" s="37" t="s">
@@ -7075,33 +8019,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="119" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="G2" s="120" t="s">
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="G2" s="119" t="s">
         <v>145</v>
       </c>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="M2" s="114" t="s">
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="M2" s="122" t="s">
         <v>146</v>
       </c>
-      <c r="N2" s="114"/>
+      <c r="N2" s="122"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="122"/>
+      <c r="B3" s="121"/>
       <c r="C3" s="12">
         <v>80000</v>
       </c>
-      <c r="G3" s="121" t="s">
+      <c r="G3" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="122"/>
+      <c r="H3" s="121"/>
       <c r="I3" s="12">
         <v>80000</v>
       </c>
@@ -7145,21 +8089,21 @@
       <c r="A5" s="5">
         <v>44018</v>
       </c>
-      <c r="B5" s="68">
+      <c r="B5" s="67">
         <v>80000</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
-      <c r="D5" s="115" t="s">
+      <c r="D5" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="112"/>
-      <c r="F5" s="116"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="114"/>
       <c r="G5" s="5">
         <v>44018</v>
       </c>
-      <c r="H5" s="68">
+      <c r="H5" s="67">
         <v>80000</v>
       </c>
       <c r="I5" s="4">
@@ -7177,21 +8121,21 @@
       <c r="A6" s="21">
         <v>44044</v>
       </c>
-      <c r="B6" s="68">
+      <c r="B6" s="67">
         <v>80000</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
-      <c r="D6" s="115" t="s">
+      <c r="D6" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E6" s="112"/>
-      <c r="F6" s="116"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="114"/>
       <c r="G6" s="21">
         <v>44044</v>
       </c>
-      <c r="H6" s="68">
+      <c r="H6" s="67">
         <v>80000</v>
       </c>
       <c r="I6" s="4">
@@ -7208,21 +8152,21 @@
       <c r="A7" s="21">
         <v>44081</v>
       </c>
-      <c r="B7" s="68">
+      <c r="B7" s="67">
         <v>80000</v>
       </c>
       <c r="C7" s="4">
         <v>3</v>
       </c>
-      <c r="D7" s="115" t="s">
+      <c r="D7" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E7" s="112"/>
-      <c r="F7" s="116"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="114"/>
       <c r="G7" s="21">
         <v>44081</v>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="67">
         <v>80000</v>
       </c>
       <c r="I7" s="4">
@@ -7239,21 +8183,21 @@
       <c r="A8" s="21">
         <v>44111</v>
       </c>
-      <c r="B8" s="68">
+      <c r="B8" s="67">
         <v>80000</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
-      <c r="D8" s="115" t="s">
+      <c r="D8" s="112" t="s">
         <v>154</v>
       </c>
-      <c r="E8" s="112"/>
-      <c r="F8" s="116"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="114"/>
       <c r="G8" s="21">
         <v>44111</v>
       </c>
-      <c r="H8" s="68">
+      <c r="H8" s="67">
         <v>80000</v>
       </c>
       <c r="I8" s="4">
@@ -7270,21 +8214,21 @@
       <c r="A9" s="21">
         <v>44142</v>
       </c>
-      <c r="B9" s="68">
+      <c r="B9" s="67">
         <v>80000</v>
       </c>
       <c r="C9" s="4">
         <v>5</v>
       </c>
-      <c r="D9" s="115" t="s">
+      <c r="D9" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E9" s="112"/>
-      <c r="F9" s="116"/>
+      <c r="E9" s="113"/>
+      <c r="F9" s="114"/>
       <c r="G9" s="21">
         <v>44142</v>
       </c>
-      <c r="H9" s="68">
+      <c r="H9" s="67">
         <v>80000</v>
       </c>
       <c r="I9" s="4">
@@ -7302,21 +8246,21 @@
       <c r="A10" s="21">
         <v>44182</v>
       </c>
-      <c r="B10" s="68">
+      <c r="B10" s="67">
         <v>80000</v>
       </c>
       <c r="C10" s="4">
         <v>6</v>
       </c>
-      <c r="D10" s="115" t="s">
+      <c r="D10" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E10" s="112"/>
-      <c r="F10" s="116"/>
+      <c r="E10" s="113"/>
+      <c r="F10" s="114"/>
       <c r="G10" s="21">
         <v>44182</v>
       </c>
-      <c r="H10" s="68">
+      <c r="H10" s="67">
         <v>80000</v>
       </c>
       <c r="I10" s="4">
@@ -7334,21 +8278,21 @@
       <c r="A11" s="21">
         <v>44209</v>
       </c>
-      <c r="B11" s="68">
+      <c r="B11" s="67">
         <v>80000</v>
       </c>
       <c r="C11" s="4">
         <v>7</v>
       </c>
-      <c r="D11" s="115" t="s">
+      <c r="D11" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E11" s="112"/>
-      <c r="F11" s="116"/>
+      <c r="E11" s="113"/>
+      <c r="F11" s="114"/>
       <c r="G11" s="21">
         <v>44209</v>
       </c>
-      <c r="H11" s="68">
+      <c r="H11" s="67">
         <v>80000</v>
       </c>
       <c r="I11" s="4">
@@ -7361,21 +8305,21 @@
       <c r="A12" s="21">
         <v>44242</v>
       </c>
-      <c r="B12" s="68">
+      <c r="B12" s="67">
         <v>80000</v>
       </c>
       <c r="C12" s="4">
         <v>8</v>
       </c>
-      <c r="D12" s="115" t="s">
+      <c r="D12" s="112" t="s">
         <v>158</v>
       </c>
-      <c r="E12" s="112"/>
-      <c r="F12" s="116"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="114"/>
       <c r="G12" s="21">
         <v>44242</v>
       </c>
-      <c r="H12" s="68">
+      <c r="H12" s="67">
         <v>80000</v>
       </c>
       <c r="I12" s="4">
@@ -7388,21 +8332,21 @@
       <c r="A13" s="21">
         <v>44248</v>
       </c>
-      <c r="B13" s="68">
+      <c r="B13" s="67">
         <v>80000</v>
       </c>
       <c r="C13" s="4">
         <v>9</v>
       </c>
-      <c r="D13" s="117" t="s">
+      <c r="D13" s="123" t="s">
         <v>159</v>
       </c>
-      <c r="E13" s="118"/>
-      <c r="F13" s="119"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="124"/>
       <c r="G13" s="21">
         <v>44248</v>
       </c>
-      <c r="H13" s="68">
+      <c r="H13" s="67">
         <v>80000</v>
       </c>
       <c r="I13" s="4">
@@ -7415,21 +8359,21 @@
       <c r="A14" s="21">
         <v>44291</v>
       </c>
-      <c r="B14" s="68">
+      <c r="B14" s="67">
         <v>80000</v>
       </c>
       <c r="C14" s="4">
         <v>10</v>
       </c>
-      <c r="D14" s="115" t="s">
+      <c r="D14" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="E14" s="112"/>
-      <c r="F14" s="116"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="114"/>
       <c r="G14" s="21">
         <v>44291</v>
       </c>
-      <c r="H14" s="68">
+      <c r="H14" s="67">
         <v>80000</v>
       </c>
       <c r="I14" s="4">
@@ -7447,21 +8391,21 @@
       <c r="A15" s="21">
         <v>44323</v>
       </c>
-      <c r="B15" s="68">
+      <c r="B15" s="67">
         <v>80000</v>
       </c>
       <c r="C15" s="4">
         <v>11</v>
       </c>
-      <c r="D15" s="115" t="s">
+      <c r="D15" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="E15" s="112"/>
-      <c r="F15" s="116"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="114"/>
       <c r="G15" s="21">
         <v>44323</v>
       </c>
-      <c r="H15" s="68">
+      <c r="H15" s="67">
         <v>80000</v>
       </c>
       <c r="I15" s="4">
@@ -7472,21 +8416,21 @@
       <c r="A16" s="21">
         <v>44355</v>
       </c>
-      <c r="B16" s="68">
+      <c r="B16" s="67">
         <v>80000</v>
       </c>
       <c r="C16" s="4">
         <v>12</v>
       </c>
-      <c r="D16" s="115" t="s">
+      <c r="D16" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="E16" s="112"/>
-      <c r="F16" s="116"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="114"/>
       <c r="G16" s="21">
         <v>44355</v>
       </c>
-      <c r="H16" s="68">
+      <c r="H16" s="67">
         <v>80000</v>
       </c>
       <c r="I16" s="4">
@@ -7497,21 +8441,21 @@
       <c r="A17" s="21">
         <v>44384</v>
       </c>
-      <c r="B17" s="68">
+      <c r="B17" s="67">
         <v>80000</v>
       </c>
       <c r="C17" s="4">
         <v>13</v>
       </c>
-      <c r="D17" s="115" t="s">
+      <c r="D17" s="112" t="s">
         <v>160</v>
       </c>
-      <c r="E17" s="112"/>
-      <c r="F17" s="116"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="114"/>
       <c r="G17" s="21">
         <v>44384</v>
       </c>
-      <c r="H17" s="68">
+      <c r="H17" s="67">
         <v>80000</v>
       </c>
       <c r="I17" s="4">
@@ -7522,21 +8466,21 @@
       <c r="A18" s="21">
         <v>44414</v>
       </c>
-      <c r="B18" s="68">
+      <c r="B18" s="67">
         <v>80000</v>
       </c>
       <c r="C18" s="4">
         <v>14</v>
       </c>
-      <c r="D18" s="115" t="s">
+      <c r="D18" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E18" s="112"/>
-      <c r="F18" s="116"/>
+      <c r="E18" s="113"/>
+      <c r="F18" s="114"/>
       <c r="G18" s="21">
         <v>44414</v>
       </c>
-      <c r="H18" s="68">
+      <c r="H18" s="67">
         <v>80000</v>
       </c>
       <c r="I18" s="4">
@@ -7547,21 +8491,21 @@
       <c r="A19" s="21">
         <v>44449</v>
       </c>
-      <c r="B19" s="68">
+      <c r="B19" s="67">
         <v>80000</v>
       </c>
       <c r="C19" s="4">
         <v>15</v>
       </c>
-      <c r="D19" s="115" t="s">
+      <c r="D19" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="116"/>
+      <c r="E19" s="113"/>
+      <c r="F19" s="114"/>
       <c r="G19" s="21">
         <v>44449</v>
       </c>
-      <c r="H19" s="68">
+      <c r="H19" s="67">
         <v>80000</v>
       </c>
       <c r="I19" s="4">
@@ -7570,20 +8514,20 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="B20" s="68">
+      <c r="B20" s="67">
         <f>251000/2</f>
         <v>125500</v>
       </c>
       <c r="C20" s="4">
         <v>16</v>
       </c>
-      <c r="D20" s="115" t="s">
+      <c r="D20" s="112" t="s">
         <v>162</v>
       </c>
-      <c r="E20" s="112"/>
-      <c r="F20" s="116"/>
+      <c r="E20" s="113"/>
+      <c r="F20" s="114"/>
       <c r="G20" s="4"/>
-      <c r="H20" s="68">
+      <c r="H20" s="67">
         <f>251000/2</f>
         <v>125500</v>
       </c>
@@ -7595,22 +8539,22 @@
       <c r="A21" s="7">
         <v>44513</v>
       </c>
-      <c r="B21" s="68">
+      <c r="B21" s="67">
         <f>B20-80000-80000</f>
         <v>-34500</v>
       </c>
       <c r="C21" s="4">
         <v>16</v>
       </c>
-      <c r="D21" s="115" t="s">
+      <c r="D21" s="112" t="s">
         <v>163</v>
       </c>
-      <c r="E21" s="112"/>
-      <c r="F21" s="116"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="114"/>
       <c r="G21" s="7">
         <v>44513</v>
       </c>
-      <c r="H21" s="68">
+      <c r="H21" s="67">
         <f>H20-80000-80000</f>
         <v>-34500</v>
       </c>
@@ -7622,21 +8566,21 @@
       <c r="A22" s="7">
         <v>44540</v>
       </c>
-      <c r="B22" s="68">
+      <c r="B22" s="67">
         <v>80000</v>
       </c>
       <c r="C22" s="4">
         <v>17</v>
       </c>
-      <c r="D22" s="115" t="s">
+      <c r="D22" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E22" s="112"/>
-      <c r="F22" s="116"/>
+      <c r="E22" s="113"/>
+      <c r="F22" s="114"/>
       <c r="G22" s="7">
         <v>44540</v>
       </c>
-      <c r="H22" s="68">
+      <c r="H22" s="67">
         <v>80000</v>
       </c>
       <c r="I22" s="4">
@@ -7647,21 +8591,21 @@
       <c r="A23" s="7">
         <v>44574</v>
       </c>
-      <c r="B23" s="68">
+      <c r="B23" s="67">
         <v>80000</v>
       </c>
       <c r="C23" s="4">
         <v>18</v>
       </c>
-      <c r="D23" s="115" t="s">
+      <c r="D23" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E23" s="112"/>
-      <c r="F23" s="116"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="114"/>
       <c r="G23" s="7">
         <v>44574</v>
       </c>
-      <c r="H23" s="68">
+      <c r="H23" s="67">
         <v>80000</v>
       </c>
       <c r="I23" s="4">
@@ -7672,21 +8616,21 @@
       <c r="A24" s="7">
         <v>44606</v>
       </c>
-      <c r="B24" s="68">
+      <c r="B24" s="67">
         <v>80000</v>
       </c>
       <c r="C24" s="4">
         <v>19</v>
       </c>
-      <c r="D24" s="115" t="s">
+      <c r="D24" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="112"/>
-      <c r="F24" s="116"/>
+      <c r="E24" s="113"/>
+      <c r="F24" s="114"/>
       <c r="G24" s="7">
         <v>44606</v>
       </c>
-      <c r="H24" s="68">
+      <c r="H24" s="67">
         <v>80000</v>
       </c>
       <c r="I24" s="4">
@@ -7697,21 +8641,21 @@
       <c r="A25" s="7">
         <v>44634</v>
       </c>
-      <c r="B25" s="68">
+      <c r="B25" s="67">
         <v>80000</v>
       </c>
       <c r="C25" s="4">
         <v>20</v>
       </c>
-      <c r="D25" s="115" t="s">
+      <c r="D25" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E25" s="112"/>
-      <c r="F25" s="116"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="114"/>
       <c r="G25" s="7">
         <v>44634</v>
       </c>
-      <c r="H25" s="68">
+      <c r="H25" s="67">
         <v>80000</v>
       </c>
       <c r="I25" s="4">
@@ -7722,21 +8666,21 @@
       <c r="A26" s="7">
         <v>44665</v>
       </c>
-      <c r="B26" s="68">
+      <c r="B26" s="67">
         <v>80000</v>
       </c>
       <c r="C26" s="4">
         <v>21</v>
       </c>
-      <c r="D26" s="115" t="s">
+      <c r="D26" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E26" s="112"/>
-      <c r="F26" s="116"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="114"/>
       <c r="G26" s="7">
         <v>44665</v>
       </c>
-      <c r="H26" s="68">
+      <c r="H26" s="67">
         <v>80000</v>
       </c>
       <c r="I26" s="4">
@@ -7750,21 +8694,21 @@
       <c r="A27" s="7">
         <v>44693</v>
       </c>
-      <c r="B27" s="68">
+      <c r="B27" s="67">
         <v>80000</v>
       </c>
       <c r="C27" s="4">
         <v>22</v>
       </c>
-      <c r="D27" s="115" t="s">
+      <c r="D27" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E27" s="112"/>
-      <c r="F27" s="116"/>
+      <c r="E27" s="113"/>
+      <c r="F27" s="114"/>
       <c r="G27" s="7">
         <v>44693</v>
       </c>
-      <c r="H27" s="68">
+      <c r="H27" s="67">
         <v>80000</v>
       </c>
       <c r="I27" s="4">
@@ -7775,21 +8719,21 @@
       <c r="A28" s="7">
         <v>44726</v>
       </c>
-      <c r="B28" s="68">
+      <c r="B28" s="67">
         <v>80000</v>
       </c>
       <c r="C28" s="4">
         <v>23</v>
       </c>
-      <c r="D28" s="115" t="s">
+      <c r="D28" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="112"/>
-      <c r="F28" s="116"/>
+      <c r="E28" s="113"/>
+      <c r="F28" s="114"/>
       <c r="G28" s="7">
         <v>44726</v>
       </c>
-      <c r="H28" s="68">
+      <c r="H28" s="67">
         <v>80000</v>
       </c>
       <c r="I28" s="4">
@@ -7800,21 +8744,21 @@
       <c r="A29" s="7">
         <v>44761</v>
       </c>
-      <c r="B29" s="68">
+      <c r="B29" s="67">
         <v>80000</v>
       </c>
       <c r="C29" s="4">
         <v>24</v>
       </c>
-      <c r="D29" s="115" t="s">
+      <c r="D29" s="112" t="s">
         <v>165</v>
       </c>
-      <c r="E29" s="112"/>
-      <c r="F29" s="116"/>
+      <c r="E29" s="113"/>
+      <c r="F29" s="114"/>
       <c r="G29" s="7">
         <v>44761</v>
       </c>
-      <c r="H29" s="68">
+      <c r="H29" s="67">
         <v>80000</v>
       </c>
       <c r="I29" s="4">
@@ -7822,68 +8766,68 @@
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="69">
+      <c r="A30" s="68">
         <v>44786</v>
       </c>
-      <c r="B30" s="70">
+      <c r="B30" s="69">
         <v>80000</v>
       </c>
-      <c r="C30" s="71">
+      <c r="C30" s="70">
         <v>25</v>
       </c>
-      <c r="D30" s="115" t="s">
+      <c r="D30" s="112" t="s">
         <v>165</v>
       </c>
-      <c r="E30" s="112"/>
-      <c r="F30" s="116"/>
-      <c r="G30" s="69">
+      <c r="E30" s="113"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="68">
         <v>44786</v>
       </c>
-      <c r="H30" s="70">
+      <c r="H30" s="69">
         <v>80000</v>
       </c>
-      <c r="I30" s="71">
+      <c r="I30" s="70">
         <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="123"/>
-      <c r="B31" s="124"/>
-      <c r="C31" s="124"/>
-      <c r="D31" s="124"/>
-      <c r="E31" s="124"/>
-      <c r="F31" s="124"/>
-      <c r="G31" s="124"/>
-      <c r="H31" s="124"/>
-      <c r="I31" s="125"/>
+      <c r="A31" s="116"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="118"/>
     </row>
     <row r="32" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="81">
+      <c r="A32" s="80">
         <v>44818</v>
       </c>
-      <c r="B32" s="72">
+      <c r="B32" s="71">
         <v>100000</v>
       </c>
-      <c r="C32" s="72">
+      <c r="C32" s="71">
         <v>1</v>
       </c>
-      <c r="D32" s="118" t="s">
+      <c r="D32" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
-      <c r="G32" s="81">
+      <c r="E32" s="115"/>
+      <c r="F32" s="115"/>
+      <c r="G32" s="80">
         <v>44818</v>
       </c>
-      <c r="H32" s="72">
+      <c r="H32" s="71">
         <v>100000</v>
       </c>
-      <c r="I32" s="72">
+      <c r="I32" s="71">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="81">
+      <c r="A33" s="80">
         <v>44841</v>
       </c>
       <c r="B33" s="4">
@@ -7892,12 +8836,12 @@
       <c r="C33" s="4">
         <v>2</v>
       </c>
-      <c r="D33" s="118" t="s">
+      <c r="D33" s="115" t="s">
         <v>167</v>
       </c>
-      <c r="E33" s="118"/>
-      <c r="F33" s="118"/>
-      <c r="G33" s="81">
+      <c r="E33" s="115"/>
+      <c r="F33" s="115"/>
+      <c r="G33" s="80">
         <v>44841</v>
       </c>
       <c r="H33" s="4">
@@ -7906,14 +8850,14 @@
       <c r="I33" s="4">
         <v>2</v>
       </c>
-      <c r="L33" s="113" t="s">
+      <c r="L33" s="126" t="s">
         <v>168</v>
       </c>
-      <c r="M33" s="113"/>
-      <c r="N33" s="113"/>
+      <c r="M33" s="126"/>
+      <c r="N33" s="126"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="81">
+      <c r="A34" s="80">
         <v>44861</v>
       </c>
       <c r="B34" s="4">
@@ -7922,12 +8866,12 @@
       <c r="C34" s="4">
         <v>3</v>
       </c>
-      <c r="D34" s="112" t="s">
+      <c r="D34" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E34" s="112"/>
-      <c r="F34" s="112"/>
-      <c r="G34" s="81">
+      <c r="E34" s="113"/>
+      <c r="F34" s="113"/>
+      <c r="G34" s="80">
         <v>44861</v>
       </c>
       <c r="H34" s="4">
@@ -7936,14 +8880,14 @@
       <c r="I34" s="4">
         <v>3</v>
       </c>
-      <c r="L34" s="113" t="s">
+      <c r="L34" s="126" t="s">
         <v>169</v>
       </c>
-      <c r="M34" s="113"/>
-      <c r="N34" s="113"/>
+      <c r="M34" s="126"/>
+      <c r="N34" s="126"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="81">
+      <c r="A35" s="80">
         <v>44893</v>
       </c>
       <c r="B35" s="4">
@@ -7952,12 +8896,12 @@
       <c r="C35" s="4">
         <v>4</v>
       </c>
-      <c r="D35" s="112" t="s">
+      <c r="D35" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E35" s="112"/>
-      <c r="F35" s="112"/>
-      <c r="G35" s="81">
+      <c r="E35" s="113"/>
+      <c r="F35" s="113"/>
+      <c r="G35" s="80">
         <v>44893</v>
       </c>
       <c r="H35" s="4">
@@ -7966,14 +8910,14 @@
       <c r="I35" s="4">
         <v>4</v>
       </c>
-      <c r="L35" s="113" t="s">
+      <c r="L35" s="126" t="s">
         <v>170</v>
       </c>
-      <c r="M35" s="113"/>
-      <c r="N35" s="113"/>
+      <c r="M35" s="126"/>
+      <c r="N35" s="126"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="81">
+      <c r="A36" s="80">
         <v>44929</v>
       </c>
       <c r="B36" s="4">
@@ -7982,12 +8926,12 @@
       <c r="C36" s="4">
         <v>5</v>
       </c>
-      <c r="D36" s="112" t="s">
+      <c r="D36" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E36" s="112"/>
-      <c r="F36" s="112"/>
-      <c r="G36" s="81">
+      <c r="E36" s="113"/>
+      <c r="F36" s="113"/>
+      <c r="G36" s="80">
         <v>44929</v>
       </c>
       <c r="H36" s="4">
@@ -7996,7 +8940,7 @@
       <c r="I36" s="4">
         <v>5</v>
       </c>
-      <c r="L36" s="82">
+      <c r="L36" s="81">
         <v>44929</v>
       </c>
       <c r="M36" s="12">
@@ -8005,12 +8949,12 @@
       <c r="N36" s="12">
         <v>1</v>
       </c>
-      <c r="O36" s="111" t="s">
+      <c r="O36" s="125" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="81">
+      <c r="A37" s="80">
         <v>44967</v>
       </c>
       <c r="B37" s="4">
@@ -8019,12 +8963,12 @@
       <c r="C37" s="4">
         <v>6</v>
       </c>
-      <c r="D37" s="112" t="s">
+      <c r="D37" s="113" t="s">
         <v>172</v>
       </c>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="81">
+      <c r="E37" s="113"/>
+      <c r="F37" s="113"/>
+      <c r="G37" s="80">
         <v>44967</v>
       </c>
       <c r="H37" s="4">
@@ -8033,7 +8977,7 @@
       <c r="I37" s="4">
         <v>6</v>
       </c>
-      <c r="L37" s="82">
+      <c r="L37" s="81">
         <v>44967</v>
       </c>
       <c r="M37" s="12">
@@ -8042,10 +8986,10 @@
       <c r="N37" s="12">
         <v>2</v>
       </c>
-      <c r="O37" s="111"/>
+      <c r="O37" s="125"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="81">
+      <c r="A38" s="80">
         <v>44995</v>
       </c>
       <c r="B38" s="4">
@@ -8054,12 +8998,12 @@
       <c r="C38" s="4">
         <v>7</v>
       </c>
-      <c r="D38" s="112" t="s">
+      <c r="D38" s="113" t="s">
         <v>173</v>
       </c>
-      <c r="E38" s="112"/>
-      <c r="F38" s="112"/>
-      <c r="G38" s="81">
+      <c r="E38" s="113"/>
+      <c r="F38" s="113"/>
+      <c r="G38" s="80">
         <v>44995</v>
       </c>
       <c r="H38" s="4">
@@ -8068,7 +9012,7 @@
       <c r="I38" s="4">
         <v>7</v>
       </c>
-      <c r="L38" s="82">
+      <c r="L38" s="81">
         <v>44995</v>
       </c>
       <c r="M38" s="12">
@@ -8077,10 +9021,10 @@
       <c r="N38" s="12">
         <v>3</v>
       </c>
-      <c r="O38" s="111"/>
+      <c r="O38" s="125"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="81">
+      <c r="A39" s="80">
         <v>45021</v>
       </c>
       <c r="B39" s="4">
@@ -8089,12 +9033,12 @@
       <c r="C39" s="4">
         <v>8</v>
       </c>
-      <c r="D39" s="112" t="s">
+      <c r="D39" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E39" s="112"/>
-      <c r="F39" s="112"/>
-      <c r="G39" s="81">
+      <c r="E39" s="113"/>
+      <c r="F39" s="113"/>
+      <c r="G39" s="80">
         <v>45021</v>
       </c>
       <c r="H39" s="4">
@@ -8103,7 +9047,7 @@
       <c r="I39" s="4">
         <v>8</v>
       </c>
-      <c r="L39" s="82">
+      <c r="L39" s="81">
         <v>45021</v>
       </c>
       <c r="M39" s="12">
@@ -8112,10 +9056,10 @@
       <c r="N39" s="12">
         <v>4</v>
       </c>
-      <c r="O39" s="111"/>
+      <c r="O39" s="125"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="81">
+      <c r="A40" s="80">
         <v>45048</v>
       </c>
       <c r="B40" s="4">
@@ -8124,12 +9068,12 @@
       <c r="C40" s="4">
         <v>9</v>
       </c>
-      <c r="D40" s="112" t="s">
+      <c r="D40" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E40" s="112"/>
-      <c r="F40" s="112"/>
-      <c r="G40" s="81">
+      <c r="E40" s="113"/>
+      <c r="F40" s="113"/>
+      <c r="G40" s="80">
         <v>45048</v>
       </c>
       <c r="H40" s="4">
@@ -8138,7 +9082,7 @@
       <c r="I40" s="4">
         <v>9</v>
       </c>
-      <c r="L40" s="82">
+      <c r="L40" s="81">
         <v>45048</v>
       </c>
       <c r="M40" s="12">
@@ -8147,10 +9091,10 @@
       <c r="N40" s="12">
         <v>5</v>
       </c>
-      <c r="O40" s="111"/>
+      <c r="O40" s="125"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="81">
+      <c r="A41" s="80">
         <v>45078</v>
       </c>
       <c r="B41" s="4">
@@ -8159,12 +9103,12 @@
       <c r="C41" s="4">
         <v>10</v>
       </c>
-      <c r="D41" s="112" t="s">
+      <c r="D41" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E41" s="112"/>
-      <c r="F41" s="112"/>
-      <c r="G41" s="81">
+      <c r="E41" s="113"/>
+      <c r="F41" s="113"/>
+      <c r="G41" s="80">
         <v>45078</v>
       </c>
       <c r="H41" s="4">
@@ -8173,7 +9117,7 @@
       <c r="I41" s="4">
         <v>10</v>
       </c>
-      <c r="L41" s="82">
+      <c r="L41" s="81">
         <v>45078</v>
       </c>
       <c r="M41" s="12">
@@ -8182,10 +9126,10 @@
       <c r="N41" s="12">
         <v>6</v>
       </c>
-      <c r="O41" s="111"/>
+      <c r="O41" s="125"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="81">
+      <c r="A42" s="80">
         <v>45113</v>
       </c>
       <c r="B42" s="4">
@@ -8194,12 +9138,12 @@
       <c r="C42" s="4">
         <v>11</v>
       </c>
-      <c r="D42" s="112" t="s">
+      <c r="D42" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E42" s="112"/>
-      <c r="F42" s="112"/>
-      <c r="G42" s="81">
+      <c r="E42" s="113"/>
+      <c r="F42" s="113"/>
+      <c r="G42" s="80">
         <v>45113</v>
       </c>
       <c r="H42" s="4">
@@ -8208,7 +9152,7 @@
       <c r="I42" s="4">
         <v>11</v>
       </c>
-      <c r="L42" s="82">
+      <c r="L42" s="81">
         <v>45113</v>
       </c>
       <c r="M42" s="12">
@@ -8217,10 +9161,10 @@
       <c r="N42" s="12">
         <v>7</v>
       </c>
-      <c r="O42" s="111"/>
+      <c r="O42" s="125"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="81">
+      <c r="A43" s="80">
         <v>45143</v>
       </c>
       <c r="B43" s="4">
@@ -8229,12 +9173,12 @@
       <c r="C43" s="4">
         <v>12</v>
       </c>
-      <c r="D43" s="112" t="s">
+      <c r="D43" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E43" s="112"/>
-      <c r="F43" s="112"/>
-      <c r="G43" s="81">
+      <c r="E43" s="113"/>
+      <c r="F43" s="113"/>
+      <c r="G43" s="80">
         <v>45143</v>
       </c>
       <c r="H43" s="4">
@@ -8243,7 +9187,7 @@
       <c r="I43" s="4">
         <v>12</v>
       </c>
-      <c r="L43" s="82">
+      <c r="L43" s="81">
         <v>45143</v>
       </c>
       <c r="M43" s="12">
@@ -8252,10 +9196,10 @@
       <c r="N43" s="12">
         <v>8</v>
       </c>
-      <c r="O43" s="111"/>
+      <c r="O43" s="125"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="81">
+      <c r="A44" s="80">
         <v>45181</v>
       </c>
       <c r="B44" s="4">
@@ -8264,12 +9208,12 @@
       <c r="C44" s="4">
         <v>13</v>
       </c>
-      <c r="D44" s="112" t="s">
+      <c r="D44" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E44" s="112"/>
-      <c r="F44" s="112"/>
-      <c r="G44" s="81">
+      <c r="E44" s="113"/>
+      <c r="F44" s="113"/>
+      <c r="G44" s="80">
         <v>45181</v>
       </c>
       <c r="H44" s="4">
@@ -8278,7 +9222,7 @@
       <c r="I44" s="4">
         <v>13</v>
       </c>
-      <c r="L44" s="82">
+      <c r="L44" s="81">
         <v>45181</v>
       </c>
       <c r="M44" s="12">
@@ -8287,10 +9231,10 @@
       <c r="N44" s="12">
         <v>9</v>
       </c>
-      <c r="O44" s="111"/>
+      <c r="O44" s="125"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="81">
+      <c r="A45" s="80">
         <v>45204</v>
       </c>
       <c r="B45" s="4">
@@ -8299,12 +9243,12 @@
       <c r="C45" s="4">
         <v>14</v>
       </c>
-      <c r="D45" s="112" t="s">
+      <c r="D45" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E45" s="112"/>
-      <c r="F45" s="112"/>
-      <c r="G45" s="81">
+      <c r="E45" s="113"/>
+      <c r="F45" s="113"/>
+      <c r="G45" s="80">
         <v>45204</v>
       </c>
       <c r="H45" s="4">
@@ -8313,7 +9257,7 @@
       <c r="I45" s="4">
         <v>14</v>
       </c>
-      <c r="L45" s="82">
+      <c r="L45" s="81">
         <v>45204</v>
       </c>
       <c r="M45" s="12">
@@ -8322,10 +9266,10 @@
       <c r="N45" s="12">
         <v>10</v>
       </c>
-      <c r="O45" s="111"/>
+      <c r="O45" s="125"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="81">
+      <c r="A46" s="80">
         <v>45239</v>
       </c>
       <c r="B46" s="4">
@@ -8334,12 +9278,12 @@
       <c r="C46" s="4">
         <v>15</v>
       </c>
-      <c r="D46" s="112" t="s">
+      <c r="D46" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E46" s="112"/>
-      <c r="F46" s="112"/>
-      <c r="G46" s="81">
+      <c r="E46" s="113"/>
+      <c r="F46" s="113"/>
+      <c r="G46" s="80">
         <v>45239</v>
       </c>
       <c r="H46" s="4">
@@ -8348,7 +9292,7 @@
       <c r="I46" s="4">
         <v>15</v>
       </c>
-      <c r="L46" s="82">
+      <c r="L46" s="81">
         <v>45239</v>
       </c>
       <c r="M46" s="12">
@@ -8357,10 +9301,10 @@
       <c r="N46" s="12">
         <v>11</v>
       </c>
-      <c r="O46" s="111"/>
+      <c r="O46" s="125"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="81">
+      <c r="A47" s="80">
         <v>45259</v>
       </c>
       <c r="B47" s="4">
@@ -8369,12 +9313,12 @@
       <c r="C47" s="4">
         <v>16</v>
       </c>
-      <c r="D47" s="112" t="s">
+      <c r="D47" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E47" s="112"/>
-      <c r="F47" s="112"/>
-      <c r="G47" s="81">
+      <c r="E47" s="113"/>
+      <c r="F47" s="113"/>
+      <c r="G47" s="80">
         <v>45259</v>
       </c>
       <c r="H47" s="4">
@@ -8383,7 +9327,7 @@
       <c r="I47" s="4">
         <v>16</v>
       </c>
-      <c r="L47" s="82">
+      <c r="L47" s="81">
         <v>45259</v>
       </c>
       <c r="M47" s="12">
@@ -8392,10 +9336,10 @@
       <c r="N47" s="12">
         <v>12</v>
       </c>
-      <c r="O47" s="111"/>
+      <c r="O47" s="125"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="81">
+      <c r="A48" s="80">
         <v>45287</v>
       </c>
       <c r="B48" s="4">
@@ -8404,12 +9348,12 @@
       <c r="C48" s="4">
         <v>17</v>
       </c>
-      <c r="D48" s="112" t="s">
+      <c r="D48" s="113" t="s">
         <v>150</v>
       </c>
-      <c r="E48" s="112"/>
-      <c r="F48" s="112"/>
-      <c r="G48" s="81">
+      <c r="E48" s="113"/>
+      <c r="F48" s="113"/>
+      <c r="G48" s="80">
         <v>45287</v>
       </c>
       <c r="H48" s="4">
@@ -8418,7 +9362,7 @@
       <c r="I48" s="4">
         <v>17</v>
       </c>
-      <c r="L48" s="81">
+      <c r="L48" s="80">
         <v>45287</v>
       </c>
       <c r="M48" s="4">
@@ -8435,11 +9379,11 @@
       <c r="C49" s="4">
         <v>18</v>
       </c>
-      <c r="D49" s="115" t="s">
+      <c r="D49" s="112" t="s">
         <v>174</v>
       </c>
-      <c r="E49" s="112"/>
-      <c r="F49" s="116"/>
+      <c r="E49" s="113"/>
+      <c r="F49" s="114"/>
       <c r="G49" s="11"/>
       <c r="H49" s="11"/>
       <c r="I49" s="4">
@@ -8456,11 +9400,11 @@
       <c r="C50" s="4">
         <v>19</v>
       </c>
-      <c r="D50" s="115" t="s">
+      <c r="D50" s="112" t="s">
         <v>174</v>
       </c>
-      <c r="E50" s="112"/>
-      <c r="F50" s="116"/>
+      <c r="E50" s="113"/>
+      <c r="F50" s="114"/>
       <c r="G50" s="11"/>
       <c r="H50" s="11"/>
       <c r="I50" s="4">
@@ -8479,9 +9423,9 @@
       <c r="C51" s="4">
         <v>20</v>
       </c>
-      <c r="D51" s="79"/>
-      <c r="E51" s="79"/>
-      <c r="F51" s="79"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="78"/>
+      <c r="F51" s="78"/>
       <c r="G51" s="4" t="s">
         <v>175</v>
       </c>
@@ -8559,14 +9503,14 @@
       <c r="O55" s="11"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="81">
+      <c r="A56" s="80">
         <v>45550</v>
       </c>
       <c r="B56" s="11"/>
       <c r="C56" s="4">
         <v>25</v>
       </c>
-      <c r="G56" s="81">
+      <c r="G56" s="80">
         <v>45550</v>
       </c>
       <c r="H56" s="11"/>
@@ -8580,6 +9524,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="O36:O47"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
     <mergeCell ref="D49:F49"/>
     <mergeCell ref="D50:F50"/>
     <mergeCell ref="D27:F27"/>
@@ -8596,45 +9579,6 @@
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="D48:F48"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="O36:O47"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -8651,15 +9595,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="97" t="s">
+      <c r="C1" s="98" t="s">
         <v>176</v>
       </c>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="100"/>
     </row>
     <row r="2" spans="3:10" x14ac:dyDescent="0.25">
       <c r="I2" t="s">
@@ -8722,7 +9666,7 @@
       <c r="C7" t="s">
         <v>182</v>
       </c>
-      <c r="F7" s="73">
+      <c r="F7" s="72">
         <v>200000</v>
       </c>
       <c r="G7" s="1">
@@ -8736,7 +9680,7 @@
       <c r="C8" t="s">
         <v>183</v>
       </c>
-      <c r="F8" s="73">
+      <c r="F8" s="72">
         <v>200000</v>
       </c>
       <c r="G8" s="1">
@@ -8750,7 +9694,7 @@
       <c r="C9" t="s">
         <v>182</v>
       </c>
-      <c r="F9" s="73">
+      <c r="F9" s="72">
         <v>200000</v>
       </c>
       <c r="G9" s="1">
@@ -8764,7 +9708,7 @@
       <c r="C10" t="s">
         <v>183</v>
       </c>
-      <c r="F10" s="73">
+      <c r="F10" s="72">
         <v>200000</v>
       </c>
       <c r="G10" s="1">
@@ -8778,7 +9722,7 @@
       <c r="C11" t="s">
         <v>184</v>
       </c>
-      <c r="F11" s="73">
+      <c r="F11" s="72">
         <v>200000</v>
       </c>
       <c r="G11" s="1">
@@ -8792,7 +9736,7 @@
       <c r="C12" t="s">
         <v>185</v>
       </c>
-      <c r="F12" s="73">
+      <c r="F12" s="72">
         <v>200000</v>
       </c>
       <c r="G12" s="1">
@@ -8806,7 +9750,7 @@
       <c r="C13" t="s">
         <v>186</v>
       </c>
-      <c r="F13" s="73">
+      <c r="F13" s="72">
         <v>200000</v>
       </c>
       <c r="G13" s="1">
@@ -8820,7 +9764,7 @@
       <c r="C14" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="73">
+      <c r="F14" s="72">
         <v>400000</v>
       </c>
       <c r="G14" s="1">
@@ -8834,7 +9778,7 @@
       <c r="C15" t="s">
         <v>186</v>
       </c>
-      <c r="F15" s="73">
+      <c r="F15" s="72">
         <v>200000</v>
       </c>
       <c r="G15" s="1">
@@ -8848,7 +9792,7 @@
       <c r="C16" t="s">
         <v>187</v>
       </c>
-      <c r="F16" s="73">
+      <c r="F16" s="72">
         <v>200000</v>
       </c>
       <c r="G16" s="1">
@@ -8862,7 +9806,7 @@
       <c r="C17" t="s">
         <v>186</v>
       </c>
-      <c r="F17" s="73">
+      <c r="F17" s="72">
         <v>200000</v>
       </c>
       <c r="G17" s="1">
@@ -8876,7 +9820,7 @@
       <c r="C18" t="s">
         <v>182</v>
       </c>
-      <c r="F18" s="73">
+      <c r="F18" s="72">
         <v>200000</v>
       </c>
       <c r="G18" s="1">
@@ -8890,7 +9834,7 @@
       <c r="C19" t="s">
         <v>186</v>
       </c>
-      <c r="F19" s="73">
+      <c r="F19" s="72">
         <v>200000</v>
       </c>
       <c r="G19" s="1">
@@ -8904,7 +9848,7 @@
       <c r="C20" t="s">
         <v>186</v>
       </c>
-      <c r="F20" s="73">
+      <c r="F20" s="72">
         <v>100000</v>
       </c>
       <c r="G20" s="1">
@@ -8918,7 +9862,7 @@
       <c r="C21" t="s">
         <v>186</v>
       </c>
-      <c r="F21" s="73">
+      <c r="F21" s="72">
         <v>100000</v>
       </c>
       <c r="G21" s="1">
@@ -8932,7 +9876,7 @@
       <c r="C22" t="s">
         <v>186</v>
       </c>
-      <c r="F22" s="73">
+      <c r="F22" s="72">
         <v>100000</v>
       </c>
       <c r="G22" s="1">
@@ -8946,7 +9890,7 @@
       <c r="C23" t="s">
         <v>186</v>
       </c>
-      <c r="F23" s="73">
+      <c r="F23" s="72">
         <v>100000</v>
       </c>
       <c r="G23" s="1">
@@ -8960,7 +9904,7 @@
       <c r="C24" t="s">
         <v>191</v>
       </c>
-      <c r="F24" s="73">
+      <c r="F24" s="72">
         <v>100000</v>
       </c>
       <c r="G24" s="1">
@@ -8974,7 +9918,7 @@
       <c r="C25" t="s">
         <v>186</v>
       </c>
-      <c r="F25" s="73">
+      <c r="F25" s="72">
         <v>200000</v>
       </c>
       <c r="G25" s="1">
@@ -8988,7 +9932,7 @@
       <c r="C26" t="s">
         <v>186</v>
       </c>
-      <c r="F26" s="73">
+      <c r="F26" s="72">
         <v>100000</v>
       </c>
       <c r="G26" s="1">
@@ -9300,7 +10244,7 @@
       <c r="S2" s="11"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="65">
+      <c r="A3" s="64">
         <v>44470</v>
       </c>
       <c r="B3" s="21">
@@ -9336,7 +10280,7 @@
       <c r="S3" s="11"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="65">
+      <c r="A4" s="64">
         <v>44470</v>
       </c>
       <c r="B4" s="21">
@@ -9372,7 +10316,7 @@
       <c r="S4" s="11"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="65">
+      <c r="A5" s="64">
         <v>44501</v>
       </c>
       <c r="B5" s="21">
@@ -9408,7 +10352,7 @@
       <c r="S5" s="11"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="65">
+      <c r="A6" s="64">
         <v>44501</v>
       </c>
       <c r="B6" s="21">
@@ -9434,7 +10378,7 @@
       <c r="S6" s="11"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="65">
+      <c r="A7" s="64">
         <v>44501</v>
       </c>
       <c r="B7" s="21">
@@ -9461,7 +10405,7 @@
       <c r="S7" s="11"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="65">
+      <c r="A8" s="64">
         <v>44501</v>
       </c>
       <c r="B8" s="21">
@@ -9483,7 +10427,7 @@
       <c r="S8" s="11"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="65">
+      <c r="A9" s="64">
         <v>44543</v>
       </c>
       <c r="B9" s="21">
@@ -9510,7 +10454,7 @@
       <c r="S9" s="11"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="65">
+      <c r="A10" s="64">
         <v>44578</v>
       </c>
       <c r="B10" s="21">
@@ -9537,7 +10481,7 @@
       <c r="S10" s="11"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="65">
+      <c r="A11" s="64">
         <v>44610</v>
       </c>
       <c r="B11" s="21">
@@ -9573,7 +10517,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="66"/>
+      <c r="A13" s="65"/>
       <c r="B13" s="1"/>
       <c r="D13">
         <f>SUM(D3:D11)-D12</f>
@@ -9625,7 +10569,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="65">
+      <c r="A17" s="64">
         <v>44470</v>
       </c>
       <c r="B17" s="21" t="s">
@@ -9669,7 +10613,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="65">
+      <c r="A18" s="64">
         <v>44470</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -9713,7 +10657,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="65">
+      <c r="A19" s="64">
         <v>44470</v>
       </c>
       <c r="B19" s="21" t="s">
@@ -9761,7 +10705,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="65">
+      <c r="A20" s="64">
         <v>44501</v>
       </c>
       <c r="B20" s="21" t="s">
@@ -9805,7 +10749,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="65">
+      <c r="A21" s="64">
         <v>44501</v>
       </c>
       <c r="B21" s="21" t="s">
@@ -9849,7 +10793,7 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="65">
+      <c r="A22" s="64">
         <v>44501</v>
       </c>
       <c r="B22" s="21" t="s">
@@ -9897,7 +10841,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="65">
+      <c r="A23" s="64">
         <v>44531</v>
       </c>
       <c r="B23" s="21" t="s">
@@ -9941,7 +10885,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="65">
+      <c r="A24" s="64">
         <v>44531</v>
       </c>
       <c r="B24" s="21" t="s">
@@ -9985,7 +10929,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="65">
+      <c r="A25" s="64">
         <v>44531</v>
       </c>
       <c r="B25" s="21" t="s">
@@ -10033,7 +10977,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="65">
+      <c r="A26" s="64">
         <v>44562</v>
       </c>
       <c r="B26" s="21" t="s">
@@ -10077,7 +11021,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="65">
+      <c r="A27" s="64">
         <v>44562</v>
       </c>
       <c r="B27" s="21" t="s">
@@ -10121,7 +11065,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="65">
+      <c r="A28" s="64">
         <v>44562</v>
       </c>
       <c r="B28" s="21" t="s">
@@ -10169,7 +11113,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="65">
+      <c r="A29" s="64">
         <v>44593</v>
       </c>
       <c r="B29" s="21" t="s">
@@ -10213,7 +11157,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="65">
+      <c r="A30" s="64">
         <v>44593</v>
       </c>
       <c r="B30" s="21" t="s">
@@ -10257,7 +11201,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="65">
+      <c r="A31" s="64">
         <v>44593</v>
       </c>
       <c r="B31" s="21" t="s">
@@ -10351,23 +11295,23 @@
       </c>
     </row>
     <row r="40" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="126" t="s">
+      <c r="A40" s="127" t="s">
         <v>262</v>
       </c>
-      <c r="B40" s="127"/>
-      <c r="C40" s="127"/>
-      <c r="D40" s="127"/>
-      <c r="E40" s="127"/>
-      <c r="F40" s="127"/>
-      <c r="G40" s="127"/>
-      <c r="H40" s="127"/>
-      <c r="I40" s="127"/>
-      <c r="J40" s="127"/>
-      <c r="K40" s="127"/>
-      <c r="L40" s="127"/>
-      <c r="M40" s="127"/>
-      <c r="N40" s="127"/>
-      <c r="O40" s="128"/>
+      <c r="B40" s="128"/>
+      <c r="C40" s="128"/>
+      <c r="D40" s="128"/>
+      <c r="E40" s="128"/>
+      <c r="F40" s="128"/>
+      <c r="G40" s="128"/>
+      <c r="H40" s="128"/>
+      <c r="I40" s="128"/>
+      <c r="J40" s="128"/>
+      <c r="K40" s="128"/>
+      <c r="L40" s="128"/>
+      <c r="M40" s="128"/>
+      <c r="N40" s="128"/>
+      <c r="O40" s="129"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
@@ -10384,7 +11328,7 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="65">
+      <c r="A43" s="64">
         <v>44621</v>
       </c>
       <c r="B43" s="21">
@@ -10398,7 +11342,7 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="65"/>
+      <c r="A44" s="64"/>
       <c r="B44" s="21"/>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
@@ -10445,7 +11389,7 @@
       </c>
     </row>
     <row r="50" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="65">
+      <c r="A50" s="64">
         <v>44621</v>
       </c>
       <c r="B50" s="21" t="s">
@@ -10489,7 +11433,7 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="65">
+      <c r="A51" s="64">
         <v>44621</v>
       </c>
       <c r="B51" s="21" t="s">
@@ -10528,15 +11472,15 @@
       <c r="L51" s="21">
         <v>44604</v>
       </c>
-      <c r="M51" s="67">
+      <c r="M51" s="66">
         <v>712.8</v>
       </c>
-      <c r="N51" s="129" t="s">
+      <c r="N51" s="130" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="65">
+      <c r="A52" s="64">
         <v>44621</v>
       </c>
       <c r="B52" s="21" t="s">
@@ -10575,13 +11519,13 @@
       <c r="L52" s="21">
         <v>44616</v>
       </c>
-      <c r="M52" s="67">
+      <c r="M52" s="66">
         <v>712.8</v>
       </c>
-      <c r="N52" s="130"/>
+      <c r="N52" s="131"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="65">
+      <c r="A53" s="64">
         <v>44593</v>
       </c>
       <c r="B53" s="21" t="s">
@@ -10619,13 +11563,13 @@
       <c r="L53" s="21">
         <v>44616</v>
       </c>
-      <c r="M53" s="67">
+      <c r="M53" s="66">
         <v>780</v>
       </c>
-      <c r="N53" s="130"/>
+      <c r="N53" s="131"/>
     </row>
     <row r="54" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="65">
+      <c r="A54" s="64">
         <v>44621</v>
       </c>
       <c r="B54" s="21" t="s">
@@ -10663,13 +11607,13 @@
       <c r="L54" s="21">
         <v>44616</v>
       </c>
-      <c r="M54" s="67">
+      <c r="M54" s="66">
         <v>780</v>
       </c>
-      <c r="N54" s="131"/>
+      <c r="N54" s="132"/>
     </row>
     <row r="55" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="65">
+      <c r="A55" s="64">
         <v>44652</v>
       </c>
       <c r="B55" s="21" t="s">
@@ -10713,7 +11657,7 @@
       </c>
     </row>
     <row r="56" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="65">
+      <c r="A56" s="64">
         <v>44652</v>
       </c>
       <c r="B56" s="21" t="s">
@@ -10752,15 +11696,15 @@
       <c r="L56" s="21">
         <v>44661</v>
       </c>
-      <c r="M56" s="67">
+      <c r="M56" s="66">
         <v>712.8</v>
       </c>
-      <c r="N56" s="132" t="s">
+      <c r="N56" s="133" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="65">
+      <c r="A57" s="64">
         <v>44652</v>
       </c>
       <c r="B57" s="21" t="s">
@@ -10799,13 +11743,13 @@
       <c r="L57" s="21">
         <v>44661</v>
       </c>
-      <c r="M57" s="67">
+      <c r="M57" s="66">
         <v>712.8</v>
       </c>
-      <c r="N57" s="133"/>
+      <c r="N57" s="134"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="65">
+      <c r="A58" s="64">
         <v>44652</v>
       </c>
       <c r="B58" s="21" t="s">
@@ -10842,13 +11786,13 @@
       <c r="L58" s="21">
         <v>44661</v>
       </c>
-      <c r="M58" s="67">
+      <c r="M58" s="66">
         <v>780</v>
       </c>
-      <c r="N58" s="133"/>
+      <c r="N58" s="134"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="65">
+      <c r="A59" s="64">
         <v>44682</v>
       </c>
       <c r="B59" s="21" t="s">
@@ -10889,10 +11833,10 @@
       <c r="M59" s="11">
         <v>1773.8</v>
       </c>
-      <c r="N59" s="133"/>
+      <c r="N59" s="134"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="65">
+      <c r="A60" s="64">
         <v>44682</v>
       </c>
       <c r="B60" s="21" t="s">
@@ -10930,13 +11874,13 @@
       <c r="L60" s="21">
         <v>44691</v>
       </c>
-      <c r="M60" s="67">
+      <c r="M60" s="66">
         <v>712.8</v>
       </c>
-      <c r="N60" s="133"/>
+      <c r="N60" s="134"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="65">
+      <c r="A61" s="64">
         <v>44682</v>
       </c>
       <c r="B61" s="21" t="s">
@@ -10974,13 +11918,13 @@
       <c r="L61" s="21">
         <v>44691</v>
       </c>
-      <c r="M61" s="67">
+      <c r="M61" s="66">
         <v>712.8</v>
       </c>
-      <c r="N61" s="133"/>
+      <c r="N61" s="134"/>
     </row>
     <row r="62" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="65">
+      <c r="A62" s="64">
         <v>44682</v>
       </c>
       <c r="B62" s="21" t="s">
@@ -11017,13 +11961,13 @@
       <c r="L62" s="21">
         <v>44691</v>
       </c>
-      <c r="M62" s="67">
+      <c r="M62" s="66">
         <v>780</v>
       </c>
-      <c r="N62" s="134"/>
+      <c r="N62" s="135"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="65">
+      <c r="A63" s="64">
         <v>44713</v>
       </c>
       <c r="B63" s="21" t="s">
@@ -11064,10 +12008,10 @@
       <c r="M63" s="11">
         <v>1773.48</v>
       </c>
-      <c r="N63" s="86"/>
+      <c r="N63" s="85"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="65">
+      <c r="A64" s="64">
         <v>44713</v>
       </c>
       <c r="B64" s="21" t="s">
@@ -11105,13 +12049,13 @@
       <c r="L64" s="21">
         <v>44722</v>
       </c>
-      <c r="M64" s="67">
+      <c r="M64" s="66">
         <v>760</v>
       </c>
-      <c r="N64" s="86"/>
+      <c r="N64" s="85"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="65">
+      <c r="A65" s="64">
         <v>44713</v>
       </c>
       <c r="B65" s="21" t="s">
@@ -11149,13 +12093,13 @@
       <c r="L65" s="21">
         <v>44722</v>
       </c>
-      <c r="M65" s="67">
+      <c r="M65" s="66">
         <v>760</v>
       </c>
-      <c r="N65" s="86"/>
+      <c r="N65" s="85"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="65">
+      <c r="A66" s="64">
         <v>44713</v>
       </c>
       <c r="B66" s="21" t="s">
@@ -11194,10 +12138,10 @@
       <c r="M66" s="11">
         <v>780</v>
       </c>
-      <c r="N66" s="86"/>
+      <c r="N66" s="85"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="65">
+      <c r="A67" s="64">
         <v>44743</v>
       </c>
       <c r="B67" s="21" t="s">
@@ -11238,10 +12182,10 @@
       <c r="M67" s="11">
         <v>1803.29</v>
       </c>
-      <c r="N67" s="86"/>
+      <c r="N67" s="85"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="65">
+      <c r="A68" s="64">
         <v>44743</v>
       </c>
       <c r="B68" s="21" t="s">
@@ -11282,10 +12226,10 @@
       <c r="M68" s="11">
         <v>760</v>
       </c>
-      <c r="N68" s="86"/>
+      <c r="N68" s="85"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="65">
+      <c r="A69" s="64">
         <v>44743</v>
       </c>
       <c r="B69" s="21" t="s">
@@ -11324,10 +12268,10 @@
       <c r="M69" s="11">
         <v>780</v>
       </c>
-      <c r="N69" s="86"/>
+      <c r="N69" s="85"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="65"/>
+      <c r="A70" s="64"/>
       <c r="B70" s="21"/>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
@@ -11340,7 +12284,7 @@
       <c r="K70" s="11"/>
       <c r="L70" s="21"/>
       <c r="M70" s="11"/>
-      <c r="N70" s="86"/>
+      <c r="N70" s="85"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="11"/>
@@ -11540,7 +12484,7 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="79"/>
+    <col min="1" max="1" width="9.140625" style="78"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -11550,28 +12494,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="137" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="136" t="s">
         <v>286</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-    </row>
-    <row r="3" spans="1:7" s="79" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
+      <c r="G2" s="136"/>
+    </row>
+    <row r="3" spans="1:7" s="78" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>287</v>
       </c>
@@ -11733,18 +12677,18 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="138" t="s">
         <v>302</v>
       </c>
-      <c r="B10" s="138"/>
-      <c r="C10" s="138"/>
-      <c r="D10" s="139"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="80">
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="140"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="79">
         <f>SUM(F4:F9)</f>
         <v>1800000</v>
       </c>
-      <c r="G10" s="80">
+      <c r="G10" s="79">
         <f>SUM(G4:G9)</f>
         <v>17536</v>
       </c>
@@ -11765,7 +12709,7 @@
   <dimension ref="A2:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" style="79" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" style="78" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" customWidth="1"/>
     <col min="4" max="4" width="27.5703125" customWidth="1"/>
@@ -11795,7 +12739,7 @@
       <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="82" t="s">
         <v>305</v>
       </c>
       <c r="C3" s="22" t="s">
@@ -11815,7 +12759,7 @@
       <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="82" t="s">
         <v>309</v>
       </c>
       <c r="C4" s="22" t="s">
@@ -11835,7 +12779,7 @@
       <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="82" t="s">
         <v>309</v>
       </c>
       <c r="C5" s="22" t="s">
@@ -11855,7 +12799,7 @@
       <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="82" t="s">
         <v>311</v>
       </c>
       <c r="C6" s="22" t="s">
@@ -11875,7 +12819,7 @@
       <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="82" t="s">
         <v>312</v>
       </c>
       <c r="C7" s="22" t="s">
@@ -11895,7 +12839,7 @@
       <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="82" t="s">
         <v>312</v>
       </c>
       <c r="C8" s="22" t="s">
@@ -11915,7 +12859,7 @@
       <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="84">
+      <c r="B9" s="83">
         <v>45326</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -11935,7 +12879,7 @@
       <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="84">
+      <c r="B10" s="83">
         <v>45326</v>
       </c>
       <c r="C10" s="22" t="s">
@@ -11955,7 +12899,7 @@
       <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="84">
+      <c r="B11" s="83">
         <v>45416</v>
       </c>
       <c r="C11" s="22" t="s">
@@ -11975,7 +12919,7 @@
       <c r="A12" s="4">
         <v>10</v>
       </c>
-      <c r="B12" s="84">
+      <c r="B12" s="83">
         <v>45630</v>
       </c>
       <c r="C12" s="22" t="s">
@@ -11995,7 +12939,7 @@
       <c r="A13" s="4">
         <v>11</v>
       </c>
-      <c r="B13" s="84" t="s">
+      <c r="B13" s="83" t="s">
         <v>315</v>
       </c>
       <c r="C13" s="22" t="s">
@@ -12015,7 +12959,7 @@
       <c r="A14" s="4">
         <v>12</v>
       </c>
-      <c r="B14" s="84" t="s">
+      <c r="B14" s="83" t="s">
         <v>319</v>
       </c>
       <c r="C14" s="22" t="s">
@@ -12035,7 +12979,7 @@
       <c r="A15" s="4">
         <v>13</v>
       </c>
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="83" t="s">
         <v>319</v>
       </c>
       <c r="C15" s="22" t="s">
@@ -12055,7 +12999,7 @@
       <c r="A16" s="4">
         <v>14</v>
       </c>
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="83" t="s">
         <v>321</v>
       </c>
       <c r="C16" s="22" t="s">
@@ -12075,7 +13019,7 @@
       <c r="A17" s="4">
         <v>15</v>
       </c>
-      <c r="B17" s="84" t="s">
+      <c r="B17" s="83" t="s">
         <v>321</v>
       </c>
       <c r="C17" s="22" t="s">
@@ -12095,7 +13039,7 @@
       <c r="A18" s="4">
         <v>16</v>
       </c>
-      <c r="B18" s="84" t="s">
+      <c r="B18" s="83" t="s">
         <v>324</v>
       </c>
       <c r="C18" s="22" t="s">
@@ -12115,7 +13059,7 @@
       <c r="A19" s="4">
         <v>17</v>
       </c>
-      <c r="B19" s="84" t="s">
+      <c r="B19" s="83" t="s">
         <v>324</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -12135,7 +13079,7 @@
       <c r="A20" s="4">
         <v>18</v>
       </c>
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="83" t="s">
         <v>326</v>
       </c>
       <c r="C20" s="22" t="s">
@@ -12155,39 +13099,39 @@
       <c r="A21" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="B21" s="120">
+      <c r="B21" s="119">
         <f>SUM(E3:E20)</f>
         <v>6600000</v>
       </c>
-      <c r="C21" s="120"/>
-      <c r="D21" s="120"/>
-      <c r="E21" s="120"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
       <c r="F21" s="11"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B22" s="143">
+      <c r="B22" s="144">
         <f>255*25900</f>
         <v>6604500</v>
       </c>
-      <c r="C22" s="143"/>
-      <c r="D22" s="143"/>
-      <c r="E22" s="143"/>
+      <c r="C22" s="144"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="144"/>
       <c r="F22" s="11"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="B23" s="144">
+      <c r="B23" s="145">
         <f>B22-B21</f>
         <v>4500</v>
       </c>
-      <c r="C23" s="144"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
       <c r="F23" s="11" t="s">
         <v>330</v>
       </c>
@@ -12196,47 +13140,47 @@
       <c r="A26" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B26" s="113">
+      <c r="B26" s="126">
         <f>255*25900</f>
         <v>6604500</v>
       </c>
-      <c r="C26" s="113"/>
-      <c r="D26" s="113"/>
-      <c r="E26" s="113"/>
+      <c r="C26" s="126"/>
+      <c r="D26" s="126"/>
+      <c r="E26" s="126"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="B27" s="113">
+      <c r="B27" s="126">
         <v>200000</v>
       </c>
-      <c r="C27" s="113"/>
-      <c r="D27" s="113"/>
-      <c r="E27" s="113"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="126"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B28" s="113">
+      <c r="B28" s="126">
         <v>60000</v>
       </c>
-      <c r="C28" s="113"/>
-      <c r="D28" s="113"/>
-      <c r="E28" s="113"/>
+      <c r="C28" s="126"/>
+      <c r="D28" s="126"/>
+      <c r="E28" s="126"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="B29" s="140">
+      <c r="B29" s="141">
         <f>SUM(B26:E28)</f>
         <v>6864500</v>
       </c>
-      <c r="C29" s="141"/>
-      <c r="D29" s="141"/>
-      <c r="E29" s="142"/>
+      <c r="C29" s="142"/>
+      <c r="D29" s="142"/>
+      <c r="E29" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -12250,4 +13194,10 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{3b17afdc-1639-4c16-803b-66671fba3b73}" enabled="1" method="Privileged" siteId="{9e52d672-a711-4a65-ad96-286a3703d96e}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>